--- a/prompt/rmyy_example.xlsx
+++ b/prompt/rmyy_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\LLM_with_RAG\prompt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ccef913d940eabb3/产品项目/LLM_service/prompt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E2A52CC-F953-4851-B0F2-6E578223B428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{4960F66C-619C-4BC3-A58E-945276A0CCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{517A9747-4D2C-4B5F-9A23-95C26096BFAC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7818D8DB-7FB3-4F53-A433-EC8D9AAFA1D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{04117A5C-B10E-4A40-B98A-F25714476F7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,38 +36,1119 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>统计最近三个月的CT检查总收入，每个月分开统计</t>
-  </si>
-  <si>
-    <t>SELECT DATEPART(MONTH, StudyDateTime) AS Month, SUM(Charge) AS TotalCharge FROM tAllReportInfo WHERE DATEPART(YEAR, StudyDateTime) = YEAR(GETDATE()) AND
-   DATEPART(MONTH, StudyDateTime) IN (MONTH(GETDATE()) - 2, MONTH(GETDATE()) - 1, MONTH(GETDATE())) AND 
-   ModalityType ='CT' AND ModalityName NOT LIKE 'LH%'" 
-   GROUP BY
-   DATEPART(MONTH, StudyDateTime)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>统计最近三个月体检患者费用占全部费用的百分比，按月分开统计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT  DATEPART(MONTH, StudyDateTime) AS Month, 
-   SUM(Charge) AS TotalCharge,
-   (SUM(CASE WHEN PatientType = '体检' THEN Charge ELSE 0 END) / SUM(Charge)) * 100 AS PercentageOfTotal
-   FROM tAllReportInfo WHERE StudyDateTime &gt;= DATEADD(MONTH, -3, GETDATE()) AND
-   ModalityType IN ('CT', 'DR', 'MR', 'MG') AND
-   ModalityName NOT LIKE 'LH%'
-   GROUP BY DATEPART(MONTH, StudyDateTime);</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+  <si>
+    <t>统计技术员:张三 在2024年全年的检查患者总人次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT  COUNT(DISTINCT ro.AccNo) AS TotalVisits
+FROM tRegProcedure rp
+JOIN tRegorder ro ON rp.OrderGuid = ro.OrderGuid
+JOIN tUser u ON rp.Technician = u.UserGuid
+WHERE u.DisplayName = '张三'
+AND YEAR(ro.InternalOptional1) = 2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 3 
+    u.DisplayName AS DoctorName,
+    COUNT(rp.CheckingItem) AS TotalCheckingItems
+FROM 
+    tReport r
+JOIN 
+    tUser u ON r.Submitter = u.UserGuid
+JOIN 
+    tRegProcedure rp ON r.ReportGuid = rp.ReportGuid
+WHERE 
+    YEAR(r.CreateDt) = 2024
+    AND rp.Modality NOT LIKE 'LH%'
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    TotalCheckingItems DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年报告医生工作量（部位数）的前三名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 3 
+    u.DisplayName AS DoctorName,
+    COUNT(DISTINCT ro.AccNo) AS TotalVisits
+FROM 
+    tReport r
+JOIN 
+    tUser u ON r.FirstApprover = u.UserGuid
+JOIN 
+    tRegProcedure rp ON r.ReportGuid = rp.ReportGuid
+JOIN 
+    tRegorder ro ON rp.OrderGuid = ro.OrderGuid
+WHERE 
+    YEAR(r.FirstApproveDt) = 2024
+    AND rp.Modality NOT LIKE 'LH%'
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    TotalVisits DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年审核医生工作量（人次数）的前三名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计最近三个月中，MR检查总费用排名最高的三个申请科室，每个月分开统计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WITH MonthlyStats AS (
+    SELECT 
+        ro.ApplyDept,
+        DATEPART(YEAR, ro.InternalOptional1) AS Year,
+        DATEPART(MONTH, ro.InternalOptional1) AS Month,
+        SUM(ro.Totalfee) AS TotalFees
+    FROM 
+        tRegorder ro
+    JOIN 
+        tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+    WHERE 
+        rp.ModalityType = 'MR'
+        AND rp.Modality NOT LIKE 'LH%'
+        AND ro.InternalOptional1 &gt;= DATEADD(MONTH, -3, GETDATE())
+    GROUP BY 
+        ro.ApplyDept, 
+        DATEPART(YEAR, ro.InternalOptional1), 
+        DATEPART(MONTH, ro.InternalOptional1)
+)
+SELECT 
+    ApplyDept,
+    Year,
+    Month,
+    TotalFees
+FROM (
+    SELECT 
+        ApplyDept,
+        Year,
+        Month,
+        TotalFees,
+        ROW_NUMBER() OVER (PARTITION BY Year, Month ORDER BY TotalFees DESC) AS Rank
+    FROM 
+        MonthlyStats
+) AS RankedStats
+WHERE 
+    Rank &lt;= 3
+ORDER BY 
+    Year DESC, 
+    Month DESC, 
+    TotalFees DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计最近三个季度中，急诊CT的每日平均检查人次，每个季度分开统计</t>
+  </si>
+  <si>
+    <t>WITH QuarterlyStats AS (
+    SELECT 
+        DATEPART(YEAR, rp.ExamineDt) AS Year,
+        DATEPART(QUARTER, rp.ExamineDt) AS Quarter,
+        CAST(rp.ExamineDt AS DATE) AS ExamDate,
+        COUNT(DISTINCT ro.AccNo) AS DailyVisits
+    FROM 
+        tRegorder ro
+    JOIN 
+        tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+    WHERE 
+        rp.ModalityType = 'CT'
+        AND ro.PatientType IN ('门诊急诊', '住院急诊', '绿色通道')
+        AND rp.Modality NOT LIKE 'LH%'
+        AND rp.ExamineDt &gt;= DATEADD(QUARTER, -3, DATEADD(QUARTER, DATEDIFF(QUARTER, 0, GETDATE()), 0))
+    GROUP BY 
+        DATEPART(YEAR, rp.ExamineDt),
+        DATEPART(QUARTER, rp.ExamineDt),
+        CAST(rp.ExamineDt AS DATE)
+)
+SELECT 
+    Year,
+    Quarter,
+    AVG(DailyVisits) AS AvgDailyVisits
+FROM 
+    QuarterlyStats
+GROUP BY 
+    Year, 
+    Quarter
+ORDER BY 
+    Year DESC, 
+    Quarter DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计最近三个季度中，急诊CT的每个工作日的平均检查人次，每个季度分开统计。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WITH QuarterlyStats AS (
+    SELECT 
+        DATEPART(YEAR, rp.ExamineDt) AS Year,
+        DATEPART(QUARTER, rp.ExamineDt) AS Quarter,
+        CAST(rp.ExamineDt AS DATE) AS ExamDate,
+        COUNT(DISTINCT ro.AccNo) AS DailyVisits
+    FROM 
+        tRegorder ro
+    JOIN 
+        tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+    WHERE 
+        rp.ModalityType = 'CT'
+        AND ro.PatientType IN ('门诊急诊', '住院急诊', '绿色通道')
+        AND rp.Modality NOT LIKE 'LH%'
+        AND rp.ExamineDt &gt;= DATEADD(QUARTER, -3, DATEADD(QUARTER, DATEDIFF(QUARTER, 0, GETDATE()), 0))
+        AND DATEPART(WEEKDAY, rp.ExamineDt) BETWEEN 2 AND 6 -- Monday to Friday
+    GROUP BY 
+        DATEPART(YEAR, rp.ExamineDt),
+        DATEPART(QUARTER, rp.ExamineDt),
+        CAST(rp.ExamineDt AS DATE)
+)
+SELECT 
+    Year,
+    Quarter,
+    AVG(DailyVisits) AS AvgDailyVisits
+FROM 
+    QuarterlyStats
+GROUP BY 
+    Year, 
+    Quarter
+ORDER BY 
+    Year DESC, 
+    Quarter DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计最近一个季度，MR检查的平均预约时长。</t>
+  </si>
+  <si>
+    <t>SELECT 
+    AVG(DATEDIFF(MINUTE, ro.InternalOptional1, rp.ExamineDt)) AS AvgAppointmentDuration
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    rp.ModalityType = 'MR'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= DATEADD(QUARTER, -1, DATEADD(QUARTER, DATEDIFF(QUARTER, 0, GETDATE()), 0))
+    AND ro.InternalOptional1 IS NOT NULL
+    AND rp.ExamineDt IS NOT NULL;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计最近一个季度，MR检查的中位数预约时长。预约时长=检查时间-申请时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WITH AppointmentDurations AS (
+    SELECT 
+        DATEDIFF(MINUTE, ro.InternalOptional1, rp.ExamineDt) AS AppointmentDuration
+    FROM 
+        tRegorder ro
+    JOIN 
+        tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+    WHERE 
+        rp.ModalityType = 'MR'
+        AND rp.Modality NOT LIKE 'LH%'
+        AND rp.ExamineDt &gt;= DATEADD(QUARTER, -1, DATEADD(QUARTER, DATEDIFF(QUARTER, 0, GETDATE()), 0))
+        AND ro.InternalOptional1 IS NOT NULL
+        AND rp.ExamineDt IS NOT NULL
+),
+RankedDurations AS (
+    SELECT 
+        AppointmentDuration,
+        ROW_NUMBER() OVER (ORDER BY AppointmentDuration) AS RowNum,
+        COUNT(*) OVER () AS TotalCount
+    FROM 
+        AppointmentDurations
+)
+SELECT 
+    AVG(AppointmentDuration) AS MedianAppointmentDuration
+FROM 
+    RankedDurations
+WHERE 
+    RowNum IN ((TotalCount + 1) / 2, (TotalCount + 2) / 2);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>统计最近六个月，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检查的平均预约时长，每个月分开统计。预约时长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检查时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>申请时间</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    DATEPART(YEAR, rp.ExamineDt) AS Year,
+    DATEPART(MONTH, rp.ExamineDt) AS Month,
+    AVG(DATEDIFF(MINUTE, ro.InternalOptional1, rp.ExamineDt)) AS AvgAppointmentDuration
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    rp.ModalityType = 'MR'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= DATEADD(MONTH, -6, GETDATE())
+    AND ro.InternalOptional1 IS NOT NULL
+    AND rp.ExamineDt IS NOT NULL
+GROUP BY 
+    DATEPART(YEAR, rp.ExamineDt),
+    DATEPART(MONTH, rp.ExamineDt)
+ORDER BY 
+    Year DESC, 
+    Month DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计最近一个月，急诊CT患者的平均检查等待时间。检查等待时间=检查时间-登记时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    AVG(DATEDIFF(MINUTE, rp.RegisterDt, rp.ExamineDt)) AS AvgWaitingTime
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    rp.ModalityType = 'CT'
+    AND ro.PatientType IN ('门诊急诊', '住院急诊', '绿色通道')
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= DATEADD(MONTH, -1, GETDATE())
+    AND rp.RegisterDt IS NOT NULL
+    AND rp.ExamineDt IS NOT NULL;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    AVG(DATEDIFF(MINUTE, rp.RegisterDt, rp.ExamineDt)) AS AvgWaitingTime
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    ro.PatientType = '住院'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= DATEADD(MONTH, -1, GETDATE())
+    AND rp.RegisterDt IS NOT NULL
+    AND rp.ExamineDt IS NOT NULL;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>统计最近一个月，住院患者的平均检查等待时间。检查等待时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检查时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>登记时间</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年6-9月，门诊MR患者的平均检查等待时间，每个月分开统计。检查等待时间=检查时间-登记时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    DATEPART(YEAR, rp.ExamineDt) AS Year,
+    DATEPART(MONTH, rp.ExamineDt) AS Month,
+    AVG(DATEDIFF(MINUTE, rp.RegisterDt, rp.ExamineDt)) AS AvgWaitingTime
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    ro.PatientType = '门诊'
+    AND rp.ModalityType = 'MR'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= '2024-06-01'
+    AND rp.ExamineDt &lt; '2024-10-01'
+    AND rp.RegisterDt IS NOT NULL
+    AND rp.ExamineDt IS NOT NULL
+GROUP BY 
+    DATEPART(YEAR, rp.ExamineDt),
+    DATEPART(MONTH, rp.ExamineDt)
+ORDER BY 
+    Year, 
+    Month;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年1-10月，MR患者的平均预约时间，每个月分开统计。预约时间=检查时间-申请时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    DATEPART(YEAR, rp.ExamineDt) AS Year,
+    DATEPART(MONTH, rp.ExamineDt) AS Month,
+    AVG(DATEDIFF(MINUTE, ro.InternalOptional1, rp.ExamineDt)) AS AvgAppointmentTime
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    rp.ModalityType = 'MR'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= '2024-01-01'
+    AND rp.ExamineDt &lt; '2024-11-01'
+    AND ro.InternalOptional1 IS NOT NULL
+    AND rp.ExamineDt IS NOT NULL
+GROUP BY 
+    DATEPART(YEAR, rp.ExamineDt),
+    DATEPART(MONTH, rp.ExamineDt)
+ORDER BY 
+    Year, 
+    Month;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询报告医生为'张三',报告结论中包含'肝癌'的所有报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 1000
+    tr.*
+FROM 
+    tReport tr
+JOIN 
+    tUser tu ON tr.Submitter = tu.UserGuid
+WHERE 
+    tu.DisplayName = '张三'
+    AND tr.WYGText LIKE '%肝癌%'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计'体检科'在2024年1-5月的检查人次，每月分开统计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    DATEPART(YEAR, rp.ExamineDt) AS Year,
+    DATEPART(MONTH, rp.ExamineDt) AS Month,
+    COUNT(DISTINCT ro.AccNo) AS NumberOfExaminations
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    ro.ApplyDept like '%体检科%'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= '2024-01-01'
+    AND rp.ExamineDt &lt; '2024-06-01'
+GROUP BY 
+    DATEPART(YEAR, rp.ExamineDt),
+    DATEPART(MONTH, rp.ExamineDt)
+ORDER BY 
+    Year, 
+    Month;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>统计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年每种设备类型的报告阳性率</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    rp.ModalityType,
+    CAST(SUM(CASE WHEN tr.IsPositive = 1 THEN 1 ELSE 0 END) AS FLOAT) / COUNT(rp.ReportGuid) * 100 AS PositiveRate
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+JOIN 
+    tReport tr ON rp.ReportGuid = tr.ReportGuid
+WHERE 
+    ro.PatientType != '体检'
+    AND YEAR(rp.ExamineDt) = 2024
+GROUP BY 
+    rp.ModalityType;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2023年每个月的检查总人次和总部位数量，每个月分开统计</t>
+  </si>
+  <si>
+    <t>SELECT 
+    DATEPART(YEAR, rp.ExamineDt) AS Year,
+    DATEPART(MONTH, rp.ExamineDt) AS Month,
+    COUNT(DISTINCT ro.AccNo) AS NumberOfExaminations,
+    COUNT(rp.CheckingItem) AS NumberOfCheckingItems
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    YEAR(rp.ExamineDt) = 2023
+    AND rp.Modality NOT LIKE 'LH%'
+GROUP BY 
+    DATEPART(YEAR, rp.ExamineDt),
+    DATEPART(MONTH, rp.ExamineDt)
+ORDER BY 
+    Year, 
+    Month;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2023年上半年每个月的CT检查总人次和总费用，每个月分开统计</t>
+  </si>
+  <si>
+    <t>SELECT 
+    DATEPART(YEAR, rp.ExamineDt) AS Year,
+    DATEPART(MONTH, rp.ExamineDt) AS Month,
+    COUNT(DISTINCT ro.AccNo) AS NumberOfExaminations,
+    SUM(ro.Totalfee) AS TotalFees
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    rp.ModalityType = 'CT'
+    AND rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= '2023-01-01'
+    AND rp.ExamineDt &lt; '2023-07-01'
+GROUP BY 
+    DATEPART(YEAR, rp.ExamineDt),
+    DATEPART(MONTH, rp.ExamineDt)
+ORDER BY 
+    Year, 
+    Month;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    rp.ModalityType,
+    SUM(ro.Totalfee) / COUNT(DISTINCT ro.AccNo) AS AverageFeePerPerson
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    YEAR(rp.ExamineDt) = 2024
+    AND rp.Modality NOT LIKE 'LH%'
+GROUP BY 
+    rp.ModalityType;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年每种设备类型的平均费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年每种设备类型的每部位平均费用</t>
+  </si>
+  <si>
+    <t>SELECT 
+    rp.ModalityType,
+    rp.CheckingItem,
+    SUM(ro.Totalfee) / COUNT(rp.CheckingItem) AS AverageFeePerCheckingItem
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    YEAR(rp.ExamineDt) = 2024
+    AND rp.Modality NOT LIKE 'LH%'
+GROUP BY 
+    rp.ModalityType,
+    rp.CheckingItem;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计每种设备类型的每位患者的平均检查部位数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    rp.ModalityType,
+    CAST(COUNT(rp.CheckingItem) AS FLOAT) / COUNT(DISTINCT ro.AccNo) AS AvgCheckingItemsPerPatient
+FROM 
+    tRegorder ro
+JOIN 
+    tRegProcedure rp ON ro.OrderGuid = rp.OrderGuid
+WHERE 
+    rp.Modality NOT LIKE 'LH%'
+    AND rp.ExamineDt &gt;= DATEADD(MONTH, -1, GETDATE())
+GROUP BY 
+    rp.ModalityType;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计胸外科的CT检查的平均费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 1000 
+    SUM(r.Totalfee) / COUNT(DISTINCT r.AccNo) AS AverageCostPerPerson
+FROM 
+    tRegorder r
+JOIN 
+    tRegProcedure p ON r.OrderGuid = p.OrderGuid
+WHERE 
+    r.ApplyDept like '%胸外科%' 
+    AND p.ModalityType = 'CT'
+    AND p.ExamineDt &gt;= DATEADD(MONTH, -1, GETDATE())</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>统计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检查平均费用最高的三个申请科室</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 3 
+    r.ApplyDept, 
+    SUM(r.Totalfee) / COUNT(DISTINCT r.AccNo) AS AverageCostPerPerson
+FROM 
+    tRegorder r
+JOIN 
+    tRegProcedure p ON r.OrderGuid = p.OrderGuid
+WHERE 
+    p.ModalityType = 'MR'
+    AND p.ExamineDt &gt;= DATEADD(MONTH, -1, GETDATE())
+GROUP BY 
+    r.ApplyDept
+ORDER BY 
+    AverageCostPerPerson DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计平均检查部位最多的前三个科室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 3 
+    r.ApplyDept, 
+    AVG(CheckingItemCounts) AS AvgCheckingItemsPerPerson
+FROM 
+    (SELECT 
+         r.ApplyDept, 
+         r.AccNo, 
+         COUNT(p.CheckingItem) AS CheckingItemCounts
+     FROM 
+         tRegorder r
+     JOIN 
+         tRegProcedure p ON r.OrderGuid = p.OrderGuid
+     WHERE 
+         p.ExamineDt &gt;= DATEADD(MONTH, -1, GETDATE())
+     GROUP BY 
+         r.ApplyDept, r.AccNo) AS SubQuery
+GROUP BY 
+    ApplyDept
+ORDER BY 
+    AvgCheckingItemsPerPerson DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年工作量最大的前10个报告医生</t>
+  </si>
+  <si>
+    <t>SELECT TOP 10 
+    u.DisplayName, 
+    COUNT(r.ReportGuid) AS Workload
+FROM 
+    tReport r
+JOIN 
+    tUser u ON r.Submitter = u.UserGuid
+WHERE 
+    YEAR(r.CreateDt) = 2024
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    Workload DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 5 
+    u.DisplayName, 
+    COUNT(r.ReportGuid) AS Workload
+FROM 
+    tReport r
+JOIN 
+    tUser u ON r.FirstApprover = u.UserGuid
+WHERE 
+    YEAR(r.FirstApproveDt) = 2023
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    Workload DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>统计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年工作量最大的前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个审核医生</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2023年工作量最大的前5个技术员</t>
+  </si>
+  <si>
+    <t>SELECT TOP 5 
+    u.DisplayName, 
+    COUNT(p.OrderGuid) AS Workload
+FROM 
+    tRegProcedure p
+JOIN 
+    tUser u ON p.Technician = u.UserGuid
+WHERE 
+    YEAR(p.ExamineDt) = 2023
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    Workload DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2023年每个科室发起的CT检查总人次数，并按照次数降序排列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询2024年第一季度平均每人次检查费用最高的前五个科室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取2023年审核报告最多的前五名医生及其审核的报告数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年各类型患者（住院、门诊等）进行MR检查的人次分布情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算2024年技术员平均每天完成的DR检查数量，并找出工作量最大的技术员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇总2023年所有急诊类型（门诊急诊、住院急诊、绿色通道）患者的CT检查费用总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分析2024年胸外科CT检查中阳性报告的比例，并列出具体数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列出2023年提交检查报告最多的前五位报告医生以及他们提交报告的总数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计2024年每种设备类型（DR, CT, MR, MG）下不同机器名称执行的检查次数，并按设备类型和次数排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询2023年到2024年间，每位审核医生报告的阳性率，并按照阳性率率从高到低排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    r.ApplyDept, 
+    COUNT(DISTINCT r.AccNo) AS TotalPersonTimes
+FROM 
+    tRegorder r
+JOIN 
+    tRegProcedure p ON r.OrderGuid = p.OrderGuid
+WHERE 
+    p.ModalityType = 'CT'
+    AND YEAR(p.ExamineDt) = 2023
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    r.ApplyDept
+ORDER BY 
+    TotalPersonTimes DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 5 
+    r.ApplyDept, 
+    AVG(r.Totalfee) / COUNT(DISTINCT r.AccNo) AS AverageCostPerPerson
+FROM 
+    tRegorder r
+JOIN 
+    tRegProcedure p ON r.OrderGuid = p.OrderGuid
+WHERE 
+    p.ExamineDt &gt;= '2024-01-01' 
+    AND p.ExamineDt &lt; '2024-04-01'
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    r.ApplyDept
+ORDER BY 
+    AverageCostPerPerson DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    r.PatientType, 
+    COUNT(DISTINCT r.AccNo) AS PersonTimes
+FROM 
+    tRegorder r
+JOIN 
+    tRegProcedure p ON r.OrderGuid = p.OrderGuid
+WHERE 
+    p.ModalityType = 'MR'
+    AND p.ExamineDt &gt;= '2024-01-01' 
+    AND p.ExamineDt &lt; '2025-01-01'
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    r.PatientType
+ORDER BY 
+    PersonTimes DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 5 
+    u.DisplayName, 
+    COUNT(r.ReportGuid) AS ReviewCount
+FROM 
+    tReport r
+JOIN 
+    tRegProcedure p ON r.ReportGuid = p.ReportGuid
+JOIN 
+    tUser u ON r.FirstApprover = u.UserGuid
+WHERE 
+    YEAR(r.FirstApproveDt) = 2023
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    ReviewCount DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WITH TechnicianWorkload AS (
+    SELECT 
+        u.UserGuid, 
+        u.DisplayName, 
+        COUNT(p.OrderGuid) AS DailyCheckCount,
+        DATEDIFF(DAY, '2024-01-01', '2025-01-01') AS DaysInYear
+    FROM 
+        tRegProcedure p
+    JOIN 
+        tUser u ON p.Technician = u.UserGuid
+    WHERE 
+        p.ModalityType = 'DR'
+        AND p.ExamineDt &gt;= '2024-01-01' 
+        AND p.ExamineDt &lt; '2025-01-01'
+        AND p.Modality NOT LIKE 'LH%'
+    GROUP BY 
+        u.UserGuid, u.DisplayName
+)
+SELECT TOP 1
+    DisplayName,
+    CAST(SUM(DailyCheckCount) AS FLOAT) / SUM(DaysInYear) AS AvgDailyChecks
+FROM 
+    TechnicianWorkload
+GROUP BY 
+    DisplayName
+ORDER BY 
+    AvgDailyChecks DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    SUM(r.Totalfee) AS TotalCTFee
+FROM 
+    tRegorder r
+JOIN 
+    tRegProcedure p ON r.OrderGuid = p.OrderGuid
+WHERE 
+    p.ModalityType = 'CT'
+    AND YEAR(p.ExamineDt) = 2023
+    AND r.PatientType IN ('门诊急诊', '住院急诊', '绿色通道')
+    AND p.Modality NOT LIKE 'LH%';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    CAST(SUM(CASE WHEN r.IsPositive = 1 THEN 1 ELSE 0 END) AS FLOAT) / COUNT(r.ReportGuid) * 100 AS PositiveRate,
+    SUM(CASE WHEN r.IsPositive = 1 THEN 1 ELSE 0 END) AS PositiveCount,
+    COUNT(r.ReportGuid) AS TotalChecks
+FROM 
+    tRegorder o
+JOIN 
+    tRegProcedure p ON o.OrderGuid = p.OrderGuid
+JOIN 
+    tReport r ON p.ReportGuid = r.ReportGuid
+WHERE 
+    o.ApplyDept = '胸外科'
+    AND p.ModalityType = 'CT'
+    AND YEAR(p.ExamineDt) = 2024
+    AND p.Modality NOT LIKE 'LH%';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT TOP 5 
+    u.DisplayName, 
+    COUNT(r.ReportGuid) AS ReportCount
+FROM 
+    tReport r
+JOIN 
+    tRegProcedure p ON r.ReportGuid = p.ReportGuid
+JOIN 
+    tUser u ON r.Submitter = u.UserGuid
+WHERE 
+    YEAR(r.CreateDt) = 2023
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    ReportCount DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    p.ModalityType, 
+    p.Modality, 
+    COUNT(p.OrderGuid) AS CheckCount
+FROM 
+    tRegProcedure p
+WHERE 
+    p.ExamineDt &gt;= '2024-01-01' 
+    AND p.ExamineDt &lt; '2025-01-01'
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    p.ModalityType, 
+    p.Modality
+ORDER BY 
+    p.ModalityType, 
+    CheckCount DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT 
+    u.DisplayName, 
+    CAST(SUM(CASE WHEN r.IsPositive = 1 THEN 1 ELSE 0 END) AS FLOAT) / COUNT(r.ReportGuid) * 100 AS PositiveRate
+FROM 
+    tReport r
+JOIN 
+    tRegProcedure p ON r.ReportGuid = p.ReportGuid
+JOIN 
+    tUser u ON r.FirstApprover = u.UserGuid
+WHERE 
+    r.FirstApproveDt &gt;= '2023-01-01' 
+    AND r.FirstApproveDt &lt; '2025-01-01'
+    AND p.Modality NOT LIKE 'LH%'
+GROUP BY 
+    u.DisplayName
+ORDER BY 
+    PositiveRate DESC;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,17 +1158,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,15 +1214,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -137,6 +1248,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,33 +1570,312 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034E7179-95B5-4A7A-926B-D824607C1F28}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92456AB3-A936-4D14-89D7-F0899B8D8EE6}">
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.125" customWidth="1"/>
-    <col min="2" max="2" width="94.125" customWidth="1"/>
+    <col min="1" max="1" width="65.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="80.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="143.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="228" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+    </row>
+    <row r="3" spans="1:2" ht="256.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="285" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="171" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="313.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="299.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="270.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="256.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="285" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="171" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="199.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="199.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="285" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="228" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="228" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="384.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="228" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="228" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="228" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="256.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>